--- a/zadani_2026/verification_plan.xlsx
+++ b/zadani_2026/verification_plan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Domin\FVS\zadani_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D506C600-097A-4DAC-8F9A-49EECCAACA4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8A5E5AD-2C54-4FFC-898E-8395D7E71884}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="36300" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VRM" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="203">
   <si>
     <t>ID</t>
   </si>
@@ -401,163 +401,460 @@
     <t>High</t>
   </si>
   <si>
-    <t>Funkčnost módů timeru</t>
-  </si>
-  <si>
-    <t>Všechny módy (DISABLED, AUTO_RESTART, ONE_SHOT, CONTINUOUS) se chovají dle specifikace</t>
-  </si>
-  <si>
-    <t>Funkční</t>
-  </si>
-  <si>
-    <t>Ano</t>
-  </si>
-  <si>
-    <t>Ověřeny všechny módy i jejich přechody</t>
-  </si>
-  <si>
-    <t>Přechody mezi módy</t>
-  </si>
-  <si>
-    <t>Přechody mezi jednotlivými módy jsou korektní</t>
-  </si>
-  <si>
-    <t>Pokryto testem mode_transition</t>
-  </si>
-  <si>
-    <t>Generování přerušení</t>
-  </si>
-  <si>
-    <t>IRQ je generováno správně při shodě cnt_reg a cmp_reg</t>
-  </si>
-  <si>
-    <t>Zohledněny rozdíly mezi módy</t>
-  </si>
-  <si>
-    <t>Přístup k registrům</t>
-  </si>
-  <si>
-    <t>Čtení a zápis do registrů funguje správně</t>
-  </si>
-  <si>
-    <t>Rozhraní</t>
-  </si>
-  <si>
-    <t>Ověřeny všechny registry</t>
-  </si>
-  <si>
-    <t>Zpracování požadavků</t>
-  </si>
-  <si>
-    <t>Všechny typy REQUEST (READ, WRITE, NONE, RESERVED) jsou správně obslouženy</t>
-  </si>
-  <si>
-    <t>Ověřeno kombinací testů</t>
-  </si>
-  <si>
-    <t>Priorita odpovědí</t>
-  </si>
-  <si>
-    <t>Signál RESPONSE odpovídá definované prioritě</t>
-  </si>
-  <si>
-    <t>IDLE, ERROR, OOR, UNALIGNED, ACK</t>
-  </si>
-  <si>
-    <t>Platnost adres</t>
-  </si>
-  <si>
-    <t>Platné, neplatné a nezarovnané adresy jsou správně zpracovány</t>
-  </si>
-  <si>
-    <t>Pokryty i hraniční případy</t>
-  </si>
-  <si>
-    <t>Chování resetu</t>
-  </si>
-  <si>
-    <t>Timer se správně chová během i po resetu</t>
-  </si>
-  <si>
-    <t>Včetně přechodů resetu</t>
-  </si>
-  <si>
-    <t>Chování cycle_cnt</t>
-  </si>
-  <si>
-    <t>Čtení a reset čítače cycle_cnt funguje správně</t>
-  </si>
-  <si>
     <t>Medium</t>
   </si>
   <si>
-    <t>Ověřeno přímými testy</t>
-  </si>
-  <si>
-    <t>Konzistence čtení po zápisu</t>
-  </si>
-  <si>
-    <t>Data přečtená po zápisu odpovídají očekávání</t>
-  </si>
-  <si>
-    <t>Ověřeno testy i ABV</t>
-  </si>
-  <si>
-    <t>Pseudo-náhodné testování</t>
-  </si>
-  <si>
-    <t>Náhodné testy respektují definovaná omezení</t>
-  </si>
-  <si>
-    <t>Verifikace</t>
-  </si>
-  <si>
-    <t>Ne</t>
-  </si>
-  <si>
-    <t>Dle zadání LAB2</t>
-  </si>
-  <si>
-    <t>Funkční pokrytí</t>
-  </si>
-  <si>
-    <t>Funkční coverage pokrývá definované scénáře</t>
-  </si>
-  <si>
-    <t>Coverage</t>
-  </si>
-  <si>
-    <t>PARTIAL</t>
-  </si>
-  <si>
-    <t>Zbývající 0,75 % odpovídá nízké pravděpodobnosti kombinací</t>
-  </si>
-  <si>
-    <t>Pokrytí kódu</t>
-  </si>
-  <si>
-    <t>Statement, branch, condition a assertion coverage</t>
-  </si>
-  <si>
-    <t>Dosaženo 100 %</t>
-  </si>
-  <si>
-    <t>Formální tvrzení</t>
-  </si>
-  <si>
-    <t>ABV tvrzení jsou správně implementována a aktivována</t>
-  </si>
-  <si>
-    <t>Dle LAB4</t>
-  </si>
-  <si>
-    <t>Shoda s referenčním modelem</t>
-  </si>
-  <si>
-    <t>Chování DUT odpovídá golden modelu</t>
-  </si>
-  <si>
-    <t>Bez rozdílů</t>
+    <t>MODE1</t>
+  </si>
+  <si>
+    <t>Check if cnt_reg does not increment when timer is set to DISABLED</t>
+  </si>
+  <si>
+    <t>DISABLED mode</t>
+  </si>
+  <si>
+    <t>MODE</t>
+  </si>
+  <si>
+    <t>disabled_t_test</t>
+  </si>
+  <si>
+    <t>random_t_test</t>
+  </si>
+  <si>
+    <t>MODE2</t>
+  </si>
+  <si>
+    <t>Check AUTO_RESTART mode: interrupt is generated and cnt_reg is restarted from zero</t>
+  </si>
+  <si>
+    <t>AUTO_RESTART mode</t>
+  </si>
+  <si>
+    <t>autorestart_t_test, timer_t_test</t>
+  </si>
+  <si>
+    <t>MODE3</t>
+  </si>
+  <si>
+    <t>Check ONE_SHOT mode: interrupt is generated, cnt_reg is restarted and timer disables itself</t>
+  </si>
+  <si>
+    <t>ONE_SHOT mode</t>
+  </si>
+  <si>
+    <t>oneshot_t_test</t>
+  </si>
+  <si>
+    <t>MODE4</t>
+  </si>
+  <si>
+    <t>Check CONTINOUS mode: interrupt is generated and cnt_reg continues running</t>
+  </si>
+  <si>
+    <t>CONTINOUS mode</t>
+  </si>
+  <si>
+    <t>continuous_t_test, mode_transition_t_test</t>
+  </si>
+  <si>
+    <t>MODE5</t>
+  </si>
+  <si>
+    <t>Check mode transitions between DISABLED, AUTO_RESTART, ONE_SHOT and CONTINOUS</t>
+  </si>
+  <si>
+    <t>Mode transitions</t>
+  </si>
+  <si>
+    <t>full_cov_t_test, addr_bus_branch_cover_t_test</t>
+  </si>
+  <si>
+    <t>MODE6</t>
+  </si>
+  <si>
+    <t>Check that IRQ can be generated in all active modes</t>
+  </si>
+  <si>
+    <t>Mode IRQ behavior</t>
+  </si>
+  <si>
+    <t>full_cov_t_test</t>
+  </si>
+  <si>
+    <t>RESET1</t>
+  </si>
+  <si>
+    <t>Check asynchronous reset initializes timer state correctly</t>
+  </si>
+  <si>
+    <t>Reset</t>
+  </si>
+  <si>
+    <t>RESET</t>
+  </si>
+  <si>
+    <t>reset_stress_t_test</t>
+  </si>
+  <si>
+    <t>RESET2</t>
+  </si>
+  <si>
+    <t>Check reset behavior during active timer operation</t>
+  </si>
+  <si>
+    <t>REG1</t>
+  </si>
+  <si>
+    <t>Check write/read access to cnt_reg</t>
+  </si>
+  <si>
+    <t>Register access</t>
+  </si>
+  <si>
+    <t>REG</t>
+  </si>
+  <si>
+    <t>timer_t_test, full_access_t_test, edge_cases_t_test</t>
+  </si>
+  <si>
+    <t>REG2</t>
+  </si>
+  <si>
+    <t>Check write/read access to cmp_reg</t>
+  </si>
+  <si>
+    <t>timer_t_test, full_access_t_test, full_cov_t_test</t>
+  </si>
+  <si>
+    <t>REG3</t>
+  </si>
+  <si>
+    <t>Check write/read access to ctrl_reg</t>
+  </si>
+  <si>
+    <t>disabled_t_test, autorestart_t_test, oneshot_t_test, continuous_t_test</t>
+  </si>
+  <si>
+    <t>REG4</t>
+  </si>
+  <si>
+    <t>Check reads from cycle_cnt low and high registers</t>
+  </si>
+  <si>
+    <t>full_access_t_test</t>
+  </si>
+  <si>
+    <t>REG5</t>
+  </si>
+  <si>
+    <t>Check writes to cycle_cnt registers are acknowledged but do not corrupt timer state</t>
+  </si>
+  <si>
+    <t>BUS1</t>
+  </si>
+  <si>
+    <t>Check CP_REQ_NONE returns CP_RSP_IDLE</t>
+  </si>
+  <si>
+    <t>Bus response</t>
+  </si>
+  <si>
+    <t>BUS</t>
+  </si>
+  <si>
+    <t>timer_t_test, continuous_t_test</t>
+  </si>
+  <si>
+    <t>BUS2</t>
+  </si>
+  <si>
+    <t>Check valid aligned read returns CP_RSP_ACK</t>
+  </si>
+  <si>
+    <t>ABV</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Verified by the directed disabled_t_test and by the scoreboard against the golden model.</t>
+  </si>
+  <si>
+    <t>Verified by autorestart_t_test; the basic AUTO_RESTART scenario is also covered by timer_t_test.</t>
+  </si>
+  <si>
+    <t>Verified by oneshot_t_test and checked by the scoreboard.</t>
+  </si>
+  <si>
+    <t>Verified by continuous_t_test; mode_transition_t_test also exercises the CONTINOUS mode.</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Mode transitions are targeted by the coverage-oriented sequences in full_cov_t_test.</t>
+  </si>
+  <si>
+    <t>timer_t_sequence_irq_modes covers AUTO_RESTART, ONE_SHOT and CONTINOUS.</t>
+  </si>
+  <si>
+    <t>Verified by reset_stress_t_test and by ABV checks for reset behavior.</t>
+  </si>
+  <si>
+    <t>The reset stress sequence toggles active and inactive reset while the timer is running.</t>
+  </si>
+  <si>
+    <t>Verified by write/read accesses and by the CNT read/write mix sequence.</t>
+  </si>
+  <si>
+    <t>Verified by setup sequences and by reading all timer registers.</t>
+  </si>
+  <si>
+    <t>Mode tests write ctrl_reg for all supported modes.</t>
+  </si>
+  <si>
+    <t>timer_t_sequence_read_all reads both TIMER_CYCLE_L and TIMER_CYCLE_H.</t>
+  </si>
+  <si>
+    <t>Covered by full_cov_t_test register accesses and checked by the scoreboard.</t>
+  </si>
+  <si>
+    <t>Run sequences use CP_REQ_NONE and ABV checks the IDLE response.</t>
+  </si>
+  <si>
+    <t>Reads from all available registers are covered by full_access_t_test.</t>
+  </si>
+  <si>
+    <t>BUS3</t>
+  </si>
+  <si>
+    <t>Check valid aligned write returns CP_RSP_ACK</t>
+  </si>
+  <si>
+    <t>timer_t_test, full_cov_t_test</t>
+  </si>
+  <si>
+    <t>Register writes are covered by the basic and coverage-oriented tests.</t>
+  </si>
+  <si>
+    <t>BUS4</t>
+  </si>
+  <si>
+    <t>Check CP_REQ_RESERVED returns CP_RSP_ERROR</t>
+  </si>
+  <si>
+    <t>edge_cases_t_test</t>
+  </si>
+  <si>
+    <t>timer_t_sequence_reserved targets the RESERVED request.</t>
+  </si>
+  <si>
+    <t>BUS5</t>
+  </si>
+  <si>
+    <t>Check address outside timer address space returns CP_RSP_OOR</t>
+  </si>
+  <si>
+    <t>timer_t_sequence_invalid_addr targets an address outside the timer address space.</t>
+  </si>
+  <si>
+    <t>BUS6</t>
+  </si>
+  <si>
+    <t>Check unaligned address returns CP_RSP_UNALIGNED</t>
+  </si>
+  <si>
+    <t>Unaligned addresses are covered by random constraints and coverage scenarios.</t>
+  </si>
+  <si>
+    <t>BUS7</t>
+  </si>
+  <si>
+    <t>Check unused aligned address inside timer address space is handled without DUT/GM mismatch</t>
+  </si>
+  <si>
+    <t>addr_bus_branch_cover_t_test</t>
+  </si>
+  <si>
+    <t>addr_bus_branch_cover_t_test was added to hit the last uncovered branch in the address decoder.</t>
+  </si>
+  <si>
+    <t>BUS8</t>
+  </si>
+  <si>
+    <t>Check CP_RSP_WAIT is never generated</t>
+  </si>
+  <si>
+    <t>ABV checks that the WAIT response is never generated.</t>
+  </si>
+  <si>
+    <t>IRQ1</t>
+  </si>
+  <si>
+    <t>Check P_IRQ is asserted when cnt_reg reaches cmp_reg in AUTO_RESTART</t>
+  </si>
+  <si>
+    <t>IRQ</t>
+  </si>
+  <si>
+    <t>autorestart_t_test</t>
+  </si>
+  <si>
+    <t>Verified by the directed AUTO_RESTART mode test and by the scoreboard.</t>
+  </si>
+  <si>
+    <t>IRQ2</t>
+  </si>
+  <si>
+    <t>Check P_IRQ is asserted when cnt_reg reaches cmp_reg in ONE_SHOT</t>
+  </si>
+  <si>
+    <t>Verified by the directed ONE_SHOT mode test and by the scoreboard.</t>
+  </si>
+  <si>
+    <t>IRQ3</t>
+  </si>
+  <si>
+    <t>Check P_IRQ is asserted when cnt_reg reaches cmp_reg in CONTINOUS</t>
+  </si>
+  <si>
+    <t>continuous_t_test</t>
+  </si>
+  <si>
+    <t>Verified by the directed CONTINOUS mode test and by the scoreboard.</t>
+  </si>
+  <si>
+    <t>IRQ4</t>
+  </si>
+  <si>
+    <t>Check P_IRQ is not generated when timer is DISABLED</t>
+  </si>
+  <si>
+    <t>Verified by disabled_t_test.</t>
+  </si>
+  <si>
+    <t>COV1</t>
+  </si>
+  <si>
+    <t>Cover all functional coverpoints and crosses used for evaluated coverage</t>
+  </si>
+  <si>
+    <t>Functional coverage</t>
+  </si>
+  <si>
+    <t>Mode, IRQ, address, request and cross coverage are covered by the coverage-oriented sequences.</t>
+  </si>
+  <si>
+    <t>COV2</t>
+  </si>
+  <si>
+    <t>Cover statements, branches, conditions and assertions in RTL</t>
+  </si>
+  <si>
+    <t>Structural coverage</t>
+  </si>
+  <si>
+    <t>full test list</t>
+  </si>
+  <si>
+    <t>The latest coverage report shows 100% assertions, branches, conditions and statements for top/HDL_DUT_U.</t>
+  </si>
+  <si>
+    <t>RAND1</t>
+  </si>
+  <si>
+    <t>Check constrained random distribution over reset, address, request and data fields</t>
+  </si>
+  <si>
+    <t>Random stimulus</t>
+  </si>
+  <si>
+    <t>RANDOM</t>
+  </si>
+  <si>
+    <t>Weights are configured in timer_t_sequence_rand according to the project assignment.</t>
+  </si>
+  <si>
+    <t>FIX1</t>
+  </si>
+  <si>
+    <t>Check RTL response decode does not update internal state on invalid accesses</t>
+  </si>
+  <si>
+    <t>RTL fix regression</t>
+  </si>
+  <si>
+    <t>RTL</t>
+  </si>
+  <si>
+    <t>edge_cases_t_test, addr_bus_branch_cover_t_test</t>
+  </si>
+  <si>
+    <t>Regression requirement after timer_fvs.vhd fixes; the scoreboard reports no mismatch.</t>
+  </si>
+  <si>
+    <t>REGMODEL1</t>
+  </si>
+  <si>
+    <t>Check register model frontdoor access through timer_reg_seq and bus adapter</t>
+  </si>
+  <si>
+    <t>Register model</t>
+  </si>
+  <si>
+    <t>REGMODEL</t>
+  </si>
+  <si>
+    <t>reg_t_test</t>
+  </si>
+  <si>
+    <t>---</t>
+  </si>
+  <si>
+    <t>reg_t_test uses m_timer_reg_block and timer_reg_seq through the same bus sequencer; it is included in sv_test_pkg.sv but not in the current test_list.</t>
+  </si>
+  <si>
+    <t>ABV1</t>
+  </si>
+  <si>
+    <t>Check formal/assertion oriented stress scenario for OOR, UNALIGNED, RESERVED, write-read and IRQ modes</t>
+  </si>
+  <si>
+    <t>ABV/Formal stress</t>
+  </si>
+  <si>
+    <t>FORMAL</t>
+  </si>
+  <si>
+    <t>formal_t_test</t>
+  </si>
+  <si>
+    <t>formal_t_test is included in sv_test_pkg.sv and an older run generated a UCDB for it; it is not in the current test_list.</t>
+  </si>
+  <si>
+    <t>SMOKE1</t>
+  </si>
+  <si>
+    <t>Check simple smoke sequence over reset and all mode set sequences</t>
+  </si>
+  <si>
+    <t>Smoke test</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>SMOKE</t>
+  </si>
+  <si>
+    <t>muj_prvni_t_test</t>
+  </si>
+  <si>
+    <t>IMPLEMENTED</t>
+  </si>
+  <si>
+    <t>A helper smoke test included in sv_test_pkg.sv; it is not part of the current regression suite.</t>
   </si>
 </sst>
 </file>
@@ -1139,8 +1436,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A2:M17" totalsRowShown="0" headerRowDxfId="9" headerRowBorderDxfId="8">
-  <autoFilter ref="A2:M17" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A2:M36" totalsRowShown="0" headerRowDxfId="9" headerRowBorderDxfId="8">
+  <autoFilter ref="A2:M36" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="REQUIREMENT " dataDxfId="7"/>
@@ -1423,10 +1720,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="61.42578125" style="8" customWidth="1"/>
+    <col min="2" max="2" width="110.140625" style="8" customWidth="1"/>
     <col min="3" max="3" width="21.28515625" style="9" customWidth="1"/>
     <col min="4" max="4" width="11.140625" customWidth="1"/>
     <col min="5" max="5" width="13.7109375" customWidth="1"/>
@@ -1437,7 +1734,7 @@
     <col min="10" max="10" width="17.5703125" style="8" customWidth="1"/>
     <col min="11" max="11" width="15.85546875" style="8" customWidth="1"/>
     <col min="12" max="12" width="23.85546875" customWidth="1"/>
-    <col min="13" max="13" width="24.42578125" customWidth="1"/>
+    <col min="13" max="13" width="48.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="14" customFormat="1">
@@ -1505,90 +1802,90 @@
       </c>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3">
+      <c r="A3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="8" t="s">
-        <v>51</v>
-      </c>
       <c r="C3" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="L3" t="s">
+        <v>15</v>
+      </c>
+      <c r="M3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" t="s">
         <v>52</v>
       </c>
-      <c r="D3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="B4" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="C4" s="9" t="s">
         <v>54</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="I3" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="J3" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="K3" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="L3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>57</v>
       </c>
       <c r="D4" t="s">
         <v>50</v>
       </c>
       <c r="E4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>54</v>
+        <v>109</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>54</v>
+        <v>109</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>54</v>
+        <v>109</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>54</v>
+        <v>109</v>
       </c>
       <c r="L4" t="s">
         <v>30</v>
       </c>
       <c r="M4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" t="s">
         <v>58</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5">
-        <v>3</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>59</v>
@@ -1600,523 +1897,1261 @@
         <v>50</v>
       </c>
       <c r="E5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>54</v>
+        <v>109</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>54</v>
+        <v>109</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>54</v>
+        <v>109</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>54</v>
+        <v>109</v>
       </c>
       <c r="L5" t="s">
         <v>30</v>
       </c>
       <c r="M5" t="s">
-        <v>61</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:13">
-      <c r="A6">
-        <v>4</v>
+      <c r="A6" t="s">
+        <v>62</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D6" t="s">
         <v>50</v>
       </c>
       <c r="E6" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>54</v>
+        <v>109</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>54</v>
+        <v>109</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>54</v>
+        <v>109</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>54</v>
+        <v>109</v>
       </c>
       <c r="L6" t="s">
         <v>30</v>
       </c>
       <c r="M6" t="s">
-        <v>65</v>
+        <v>112</v>
       </c>
     </row>
     <row r="7" spans="1:13">
-      <c r="A7">
-        <v>5</v>
+      <c r="A7" t="s">
+        <v>66</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D7" t="s">
         <v>50</v>
       </c>
       <c r="E7" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>54</v>
+        <v>109</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>54</v>
+        <v>109</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>54</v>
+        <v>109</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>54</v>
+        <v>109</v>
       </c>
       <c r="L7" t="s">
         <v>30</v>
       </c>
       <c r="M7" t="s">
-        <v>68</v>
+        <v>113</v>
       </c>
     </row>
     <row r="8" spans="1:13">
-      <c r="A8">
-        <v>6</v>
+      <c r="A8" t="s">
+        <v>70</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D8" t="s">
         <v>50</v>
       </c>
       <c r="E8" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>54</v>
+        <v>109</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>54</v>
+        <v>114</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>54</v>
+        <v>109</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>54</v>
+        <v>114</v>
       </c>
       <c r="L8" t="s">
         <v>30</v>
       </c>
       <c r="M8" t="s">
-        <v>71</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9" spans="1:13">
-      <c r="A9">
-        <v>7</v>
+      <c r="A9" t="s">
+        <v>74</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D9" t="s">
         <v>50</v>
       </c>
       <c r="E9" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>54</v>
+        <v>109</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>54</v>
+        <v>109</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>54</v>
+        <v>109</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>54</v>
+        <v>109</v>
       </c>
       <c r="L9" t="s">
         <v>30</v>
       </c>
       <c r="M9" t="s">
-        <v>74</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10">
-        <v>8</v>
+      <c r="A10" t="s">
+        <v>78</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D10" t="s">
         <v>50</v>
       </c>
       <c r="E10" t="s">
-        <v>53</v>
+        <v>81</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>54</v>
+        <v>109</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>54</v>
+        <v>109</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>54</v>
+        <v>109</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>54</v>
+        <v>109</v>
       </c>
       <c r="L10" t="s">
         <v>30</v>
       </c>
       <c r="M10" t="s">
-        <v>77</v>
+        <v>117</v>
       </c>
     </row>
     <row r="11" spans="1:13">
-      <c r="A11">
-        <v>9</v>
+      <c r="A11" t="s">
+        <v>83</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D11" t="s">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="E11" t="s">
-        <v>53</v>
+        <v>81</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>54</v>
+        <v>109</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>54</v>
+        <v>109</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>54</v>
+        <v>109</v>
       </c>
       <c r="K11" s="8" t="s">
-        <v>54</v>
+        <v>109</v>
       </c>
       <c r="L11" t="s">
         <v>30</v>
       </c>
       <c r="M11" t="s">
-        <v>81</v>
+        <v>118</v>
       </c>
     </row>
     <row r="12" spans="1:13">
-      <c r="A12">
-        <v>10</v>
+      <c r="A12" t="s">
+        <v>85</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D12" t="s">
         <v>50</v>
       </c>
       <c r="E12" t="s">
-        <v>53</v>
+        <v>88</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>54</v>
+        <v>109</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>54</v>
+        <v>109</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>54</v>
+        <v>89</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>54</v>
+        <v>109</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>54</v>
+        <v>109</v>
       </c>
       <c r="L12" t="s">
         <v>30</v>
       </c>
       <c r="M12" t="s">
-        <v>84</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" spans="1:13">
-      <c r="A13">
-        <v>11</v>
+      <c r="A13" t="s">
+        <v>90</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D13" t="s">
         <v>50</v>
       </c>
       <c r="E13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>54</v>
+        <v>109</v>
       </c>
       <c r="K13" s="8" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="L13" t="s">
         <v>30</v>
       </c>
       <c r="M13" t="s">
-        <v>89</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14" spans="1:13">
-      <c r="A14">
-        <v>12</v>
+      <c r="A14" t="s">
+        <v>93</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D14" t="s">
         <v>50</v>
       </c>
       <c r="E14" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="F14" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="L14" t="s">
+        <v>30</v>
+      </c>
+      <c r="M14" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="A15" t="s">
+        <v>96</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="D15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E15" t="s">
         <v>88</v>
       </c>
-      <c r="G14" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="H14" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="I14" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="J14" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="K14" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="L14" t="s">
-        <v>93</v>
-      </c>
-      <c r="M14" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13">
-      <c r="A15">
-        <v>13</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="D15" t="s">
-        <v>50</v>
-      </c>
-      <c r="E15" t="s">
-        <v>92</v>
-      </c>
       <c r="F15" s="8" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>54</v>
+        <v>109</v>
       </c>
       <c r="K15" s="8" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="L15" t="s">
         <v>30</v>
       </c>
       <c r="M15" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16" spans="1:13">
-      <c r="A16">
-        <v>14</v>
+      <c r="A16" t="s">
+        <v>99</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="D16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>54</v>
+        <v>114</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>54</v>
+        <v>109</v>
       </c>
       <c r="K16" s="8" t="s">
-        <v>54</v>
+        <v>114</v>
       </c>
       <c r="L16" t="s">
         <v>30</v>
       </c>
       <c r="M16" t="s">
-        <v>100</v>
+        <v>123</v>
       </c>
     </row>
     <row r="17" spans="1:13">
-      <c r="A17">
-        <v>15</v>
+      <c r="A17" t="s">
+        <v>101</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D17" t="s">
         <v>50</v>
       </c>
       <c r="E17" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>54</v>
+        <v>109</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>54</v>
+        <v>109</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>54</v>
+        <v>105</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="J17" s="8" t="s">
-        <v>54</v>
+        <v>109</v>
       </c>
       <c r="K17" s="8" t="s">
-        <v>54</v>
+        <v>109</v>
       </c>
       <c r="L17" t="s">
         <v>30</v>
       </c>
       <c r="M17" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
+      <c r="A18" t="s">
+        <v>106</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="C18" s="9" t="s">
         <v>103</v>
+      </c>
+      <c r="D18" t="s">
+        <v>50</v>
+      </c>
+      <c r="E18" t="s">
+        <v>104</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="I18" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="J18" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="K18" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="L18" t="s">
+        <v>30</v>
+      </c>
+      <c r="M18" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
+      <c r="A19" t="s">
+        <v>126</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="D19" t="s">
+        <v>50</v>
+      </c>
+      <c r="E19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="I19" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="J19" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="K19" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="L19" t="s">
+        <v>30</v>
+      </c>
+      <c r="M19" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
+      <c r="A20" t="s">
+        <v>130</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="D20" t="s">
+        <v>50</v>
+      </c>
+      <c r="E20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="I20" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="J20" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="K20" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="L20" t="s">
+        <v>30</v>
+      </c>
+      <c r="M20" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
+      <c r="A21" t="s">
+        <v>134</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="D21" t="s">
+        <v>50</v>
+      </c>
+      <c r="E21" t="s">
+        <v>104</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="I21" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="J21" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="K21" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="L21" t="s">
+        <v>30</v>
+      </c>
+      <c r="M21" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
+      <c r="A22" t="s">
+        <v>137</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="D22" t="s">
+        <v>50</v>
+      </c>
+      <c r="E22" t="s">
+        <v>104</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="I22" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="J22" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="K22" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="L22" t="s">
+        <v>30</v>
+      </c>
+      <c r="M22" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
+      <c r="A23" t="s">
+        <v>140</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="D23" t="s">
+        <v>51</v>
+      </c>
+      <c r="E23" t="s">
+        <v>104</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="I23" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="J23" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="K23" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="L23" t="s">
+        <v>30</v>
+      </c>
+      <c r="M23" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
+      <c r="A24" t="s">
+        <v>144</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="D24" t="s">
+        <v>50</v>
+      </c>
+      <c r="E24" t="s">
+        <v>104</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="I24" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="J24" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K24" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="L24" t="s">
+        <v>30</v>
+      </c>
+      <c r="M24" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13">
+      <c r="A25" t="s">
+        <v>147</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="D25" t="s">
+        <v>50</v>
+      </c>
+      <c r="E25" t="s">
+        <v>149</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="I25" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="J25" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="K25" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="L25" t="s">
+        <v>30</v>
+      </c>
+      <c r="M25" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13">
+      <c r="A26" t="s">
+        <v>152</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="D26" t="s">
+        <v>50</v>
+      </c>
+      <c r="E26" t="s">
+        <v>149</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="G26" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="H26" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="I26" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="J26" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="K26" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="L26" t="s">
+        <v>30</v>
+      </c>
+      <c r="M26" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
+      <c r="A27" t="s">
+        <v>155</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="D27" t="s">
+        <v>50</v>
+      </c>
+      <c r="E27" t="s">
+        <v>149</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="G27" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="H27" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="I27" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="J27" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="K27" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="L27" t="s">
+        <v>30</v>
+      </c>
+      <c r="M27" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13">
+      <c r="A28" t="s">
+        <v>159</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="D28" t="s">
+        <v>50</v>
+      </c>
+      <c r="E28" t="s">
+        <v>149</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="G28" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="H28" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="I28" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="J28" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="K28" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="L28" t="s">
+        <v>30</v>
+      </c>
+      <c r="M28" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13">
+      <c r="A29" t="s">
+        <v>162</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="D29" t="s">
+        <v>50</v>
+      </c>
+      <c r="E29" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G29" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H29" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I29" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="J29" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="K29" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="L29" t="s">
+        <v>30</v>
+      </c>
+      <c r="M29" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13">
+      <c r="A30" t="s">
+        <v>166</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="D30" t="s">
+        <v>50</v>
+      </c>
+      <c r="E30" t="s">
+        <v>8</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G30" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="H30" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="I30" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="J30" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K30" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="L30" t="s">
+        <v>30</v>
+      </c>
+      <c r="M30" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13">
+      <c r="A31" t="s">
+        <v>171</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="D31" t="s">
+        <v>51</v>
+      </c>
+      <c r="E31" t="s">
+        <v>174</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="G31" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H31" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="I31" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="J31" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="K31" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="L31" t="s">
+        <v>30</v>
+      </c>
+      <c r="M31" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13">
+      <c r="A32" t="s">
+        <v>176</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="D32" t="s">
+        <v>50</v>
+      </c>
+      <c r="E32" t="s">
+        <v>179</v>
+      </c>
+      <c r="F32" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="G32" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="H32" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="I32" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="J32" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="K32" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="L32" t="s">
+        <v>30</v>
+      </c>
+      <c r="M32" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13">
+      <c r="A33" t="s">
+        <v>182</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="D33" t="s">
+        <v>51</v>
+      </c>
+      <c r="E33" t="s">
+        <v>185</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="G33" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H33" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="I33" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="J33" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K33" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="L33" t="s">
+        <v>30</v>
+      </c>
+      <c r="M33" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13">
+      <c r="A34" t="s">
+        <v>189</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="D34" t="s">
+        <v>50</v>
+      </c>
+      <c r="E34" t="s">
+        <v>192</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="G34" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="H34" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="I34" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="J34" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="K34" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="L34" t="s">
+        <v>30</v>
+      </c>
+      <c r="M34" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13">
+      <c r="A35" t="s">
+        <v>195</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="D35" t="s">
+        <v>198</v>
+      </c>
+      <c r="E35" t="s">
+        <v>199</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="G35" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H35" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="I35" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="J35" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="K35" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="L35" t="s">
+        <v>201</v>
+      </c>
+      <c r="M35" t="s">
+        <v>202</v>
       </c>
     </row>
   </sheetData>
